--- a/Project/outputs/tables/table_var_metrics_h5.xlsx
+++ b/Project/outputs/tables/table_var_metrics_h5.xlsx
@@ -482,19 +482,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003734214803983991</v>
+        <v>0.003947129649199044</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03348157342487242</v>
+        <v>0.03355131164966139</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06110822206531614</v>
+        <v>0.06282618601506099</v>
       </c>
       <c r="E2" t="n">
-        <v>20.15215873208332</v>
+        <v>19.96859380006503</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4553119730185498</v>
+        <v>0.4317032040472175</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -513,23 +513,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STOXX600</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002095993049972435</v>
+        <v>0.002569085526625282</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02946592624179593</v>
+        <v>0.03377900490080622</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0457820166656345</v>
+        <v>0.05068614728528183</v>
       </c>
       <c r="E3" t="n">
-        <v>21.16718362341387</v>
+        <v>20.14196072743276</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4435075885328836</v>
+        <v>0.4249578414839797</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -548,23 +548,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FTSE100</t>
+          <t>CAC40</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001945561673631419</v>
+        <v>0.0029786349490507</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0286724106613691</v>
+        <v>0.03458342619056247</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04410852155345291</v>
+        <v>0.05457687192438478</v>
       </c>
       <c r="E4" t="n">
-        <v>18.37921806732942</v>
+        <v>21.34504880047567</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4772344013490725</v>
+        <v>0.4468802698145025</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -583,23 +583,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>FTSE100</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002461628412542051</v>
+        <v>0.001957627501627516</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03433393538307532</v>
+        <v>0.02827191522417985</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04961480033762154</v>
+        <v>0.04424508449113321</v>
       </c>
       <c r="E5" t="n">
-        <v>20.70127424666486</v>
+        <v>18.02288000296929</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4418212478920742</v>
+        <v>0.4654300168634064</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001484622760816823</v>
+        <v>0.001530217715962794</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02735310318759149</v>
+        <v>0.02797431765628816</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03853080275334039</v>
+        <v>0.03911799734090173</v>
       </c>
       <c r="E6" t="n">
-        <v>15.55633319490162</v>
+        <v>15.88839124022004</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4940978077571669</v>
+        <v>0.4974704890387858</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -653,23 +653,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HangSeng</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001316047305537059</v>
+        <v>0.002145122491121179</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02655020416339677</v>
+        <v>0.02731077884074976</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03627736629824523</v>
+        <v>0.04631546708305097</v>
       </c>
       <c r="E7" t="n">
-        <v>14.17871791757327</v>
+        <v>15.19379227958312</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4974704890387858</v>
+        <v>0.4586846543001686</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -688,23 +688,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MSCI_EM</t>
+          <t>HangSeng</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003471804117357251</v>
+        <v>0.001312925655624192</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03341393849534512</v>
+        <v>0.0263927744361105</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05892201725464982</v>
+        <v>0.03623431599498177</v>
       </c>
       <c r="E8" t="n">
-        <v>16.06672806626992</v>
+        <v>14.18850961302156</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4991568296795953</v>
+        <v>0.4738617200674536</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -723,23 +723,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CSI300</t>
+          <t>SSE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001560829142487694</v>
+        <v>0.001477532236166935</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0265406764444611</v>
+        <v>0.02424619214863524</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03950733023740904</v>
+        <v>0.03843868150921589</v>
       </c>
       <c r="E9" t="n">
-        <v>13.7345611387929</v>
+        <v>14.64446601512593</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4907251264755481</v>
+        <v>0.4721753794266442</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.002258837658291091</v>
+        <v>0.002239784465672205</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0299764710002384</v>
+        <v>0.0295137151308742</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0467313846457087</v>
+        <v>0.04655509395550139</v>
       </c>
       <c r="E10" t="n">
-        <v>17.49202187337865</v>
+        <v>17.42420530986168</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4749156829679595</v>
+        <v>0.4588954468802698</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -797,19 +797,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.001336868463761649</v>
+        <v>0.001328286972923505</v>
       </c>
       <c r="C11" t="n">
-        <v>0.02362390285492318</v>
+        <v>0.02329276322853183</v>
       </c>
       <c r="D11" t="n">
-        <v>0.03656321189066476</v>
+        <v>0.03644567152521003</v>
       </c>
       <c r="E11" t="n">
-        <v>15.14750108190887</v>
+        <v>14.8592033947343</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5037128712871287</v>
+        <v>0.5031055900621118</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -828,23 +828,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STOXX600</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.001120439623073517</v>
+        <v>0.001590508244584389</v>
       </c>
       <c r="C12" t="n">
-        <v>0.02132970605113809</v>
+        <v>0.02478063572522411</v>
       </c>
       <c r="D12" t="n">
-        <v>0.03347296854289319</v>
+        <v>0.03988117656971003</v>
       </c>
       <c r="E12" t="n">
-        <v>16.825533747723</v>
+        <v>16.18868113174356</v>
       </c>
       <c r="F12" t="n">
-        <v>0.469059405940594</v>
+        <v>0.462111801242236</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -863,23 +863,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FTSE100</t>
+          <t>CAC40</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.001132915969191167</v>
+        <v>0.001418919183874914</v>
       </c>
       <c r="C13" t="n">
-        <v>0.02038994285728336</v>
+        <v>0.02455385158696056</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0336588171092088</v>
+        <v>0.03766854369198408</v>
       </c>
       <c r="E13" t="n">
-        <v>18.33533884990208</v>
+        <v>16.79561754860348</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4727722772277227</v>
+        <v>0.4819875776397515</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -898,23 +898,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>FTSE100</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.001570285184071599</v>
+        <v>0.001138541339181364</v>
       </c>
       <c r="C14" t="n">
-        <v>0.02461253276491828</v>
+        <v>0.02009936881988246</v>
       </c>
       <c r="D14" t="n">
-        <v>0.03962682404724859</v>
+        <v>0.0337422782156357</v>
       </c>
       <c r="E14" t="n">
-        <v>16.15474206450522</v>
+        <v>17.96671718538683</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4925742574257426</v>
+        <v>0.4645962732919255</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -937,19 +937,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.003997654137029364</v>
+        <v>0.003965070261394011</v>
       </c>
       <c r="C15" t="n">
-        <v>0.03137044973175255</v>
+        <v>0.03100562850788597</v>
       </c>
       <c r="D15" t="n">
-        <v>0.06322700480830452</v>
+        <v>0.0629688038745696</v>
       </c>
       <c r="E15" t="n">
-        <v>15.08666740527755</v>
+        <v>15.01063222909721</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5074257425742574</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -968,23 +968,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HangSeng</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.003768899009889633</v>
+        <v>0.001937619856335759</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0337012317238639</v>
+        <v>0.02713045157666489</v>
       </c>
       <c r="D16" t="n">
-        <v>0.06139135940740873</v>
+        <v>0.04401840360957856</v>
       </c>
       <c r="E16" t="n">
-        <v>13.51392370004505</v>
+        <v>15.86427658220265</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5284653465346535</v>
+        <v>0.4869565217391305</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1003,23 +1003,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MSCI_EM</t>
+          <t>HangSeng</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.001589109650636309</v>
+        <v>0.003671893916472475</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0275872256103154</v>
+        <v>0.03265627327322902</v>
       </c>
       <c r="D17" t="n">
-        <v>0.03986363820120171</v>
+        <v>0.060596154304316</v>
       </c>
       <c r="E17" t="n">
-        <v>16.67028700222909</v>
+        <v>13.16294335067899</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4727722772277227</v>
+        <v>0.5279503105590062</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1038,23 +1038,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CSI300</t>
+          <t>SSE</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.00169766337319835</v>
+        <v>0.001775131176788968</v>
       </c>
       <c r="C18" t="n">
-        <v>0.02504951553480702</v>
+        <v>0.02502709899998087</v>
       </c>
       <c r="D18" t="n">
-        <v>0.04120271075060899</v>
+        <v>0.04213230561919164</v>
       </c>
       <c r="E18" t="n">
-        <v>17.06297882107554</v>
+        <v>19.07616983035012</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4987623762376238</v>
+        <v>0.484472049689441</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1077,19 +1077,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.002026729426356449</v>
+        <v>0.002103246368944423</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02595806339112522</v>
+        <v>0.02606825896479496</v>
       </c>
       <c r="D19" t="n">
-        <v>0.04362581684469241</v>
+        <v>0.04468166717627446</v>
       </c>
       <c r="E19" t="n">
-        <v>16.0996215840833</v>
+        <v>16.11553015659964</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4931930693069306</v>
+        <v>0.4916149068322981</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
